--- a/Design Files/Relay Driver-10A-v1.0/BOM/eSpark-BOM-Relay Driver-10A-v1.0.xlsx
+++ b/Design Files/Relay Driver-10A-v1.0/BOM/eSpark-BOM-Relay Driver-10A-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="469">
   <si>
     <t>Component list</t>
   </si>
@@ -405,9 +405,6 @@
     <t>TVS DIODE 5V 9.8V SOD923</t>
   </si>
   <si>
-    <t>TVS SURGE PROTECTOR 1-CH 3.3V</t>
-  </si>
-  <si>
     <t>TVS DIODE 5VWM 6.3VC DSN0603-2</t>
   </si>
   <si>
@@ -609,9 +606,6 @@
     <t>SOD-923.</t>
   </si>
   <si>
-    <t>SOD-123</t>
-  </si>
-  <si>
     <t>DSN0603-2</t>
   </si>
   <si>
@@ -762,9 +756,6 @@
     <t>ESD9L5.0ST5G</t>
   </si>
   <si>
-    <t>AZ3003-01G</t>
-  </si>
-  <si>
     <t>PESD5V0H1BSFYL</t>
   </si>
   <si>
@@ -936,9 +927,6 @@
     <t>ON Semiconductor</t>
   </si>
   <si>
-    <t>Amazing</t>
-  </si>
-  <si>
     <t>Nexperia</t>
   </si>
   <si>
@@ -1423,6 +1411,21 @@
   </si>
   <si>
     <t>C94832</t>
+  </si>
+  <si>
+    <t>20A 350W 16V 4V 3.3V SOD-323 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>SOD-323</t>
+  </si>
+  <si>
+    <t>SD03</t>
+  </si>
+  <si>
+    <t>C502526</t>
+  </si>
+  <si>
+    <t>C6961258</t>
   </si>
 </sst>
 </file>
@@ -2252,7 +2255,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="40" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -2276,7 +2279,7 @@
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="41" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="30"/>
@@ -2366,43 +2369,43 @@
         <v>108</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I7" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="O7" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="K7" s="12" t="s">
+      <c r="P7" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="L7" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="M7" s="12" t="s">
+      <c r="Q7" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="R7" s="12" t="s">
         <v>450</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="R7" s="12" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="24" x14ac:dyDescent="0.25">
@@ -2421,22 +2424,22 @@
         <v>109</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="L8" s="14">
         <v>14</v>
@@ -2449,7 +2452,7 @@
         <v>80</v>
       </c>
       <c r="O8" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P8" s="21">
         <v>1.32E-2</v>
@@ -2476,22 +2479,22 @@
         <v>110</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="L9" s="20">
         <v>2</v>
@@ -2504,7 +2507,7 @@
         <v>11</v>
       </c>
       <c r="O9" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P9" s="15">
         <v>1.0296000000000001</v>
@@ -2531,22 +2534,22 @@
         <v>111</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="L10" s="14">
         <v>2</v>
@@ -2559,7 +2562,7 @@
         <v>20</v>
       </c>
       <c r="O10" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P10" s="21">
         <v>2.2800000000000001E-2</v>
@@ -2586,22 +2589,22 @@
         <v>112</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="L11" s="20">
         <v>1</v>
@@ -2614,7 +2617,7 @@
         <v>100</v>
       </c>
       <c r="O11" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P11" s="21">
         <v>1.4E-3</v>
@@ -2641,22 +2644,22 @@
         <v>113</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K12" s="43" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="L12" s="14">
         <v>2</v>
@@ -2669,7 +2672,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P12" s="21">
         <v>1E-3</v>
@@ -2696,22 +2699,22 @@
         <v>114</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="L13" s="20">
         <v>6</v>
@@ -2724,7 +2727,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P13" s="21">
         <v>2.5999999999999999E-3</v>
@@ -2751,22 +2754,22 @@
         <v>112</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G14" s="42" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H14" s="42" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J14" s="42" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K14" s="45" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L14" s="42">
         <v>2</v>
@@ -2776,19 +2779,19 @@
         <v>10</v>
       </c>
       <c r="N14" s="42" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="O14" s="46" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P14" s="47" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="Q14" s="47" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="R14" s="48" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -2807,22 +2810,22 @@
         <v>115</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="L15" s="20">
         <v>1</v>
@@ -2835,7 +2838,7 @@
         <v>20</v>
       </c>
       <c r="O15" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P15" s="21">
         <v>2.0799999999999999E-2</v>
@@ -2862,22 +2865,22 @@
         <v>116</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="L16" s="14">
         <v>2</v>
@@ -2890,7 +2893,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P16" s="15">
         <v>1E-3</v>
@@ -2917,22 +2920,22 @@
         <v>117</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="L17" s="20">
         <v>4</v>
@@ -2945,7 +2948,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P17" s="15">
         <v>1.6000000000000001E-3</v>
@@ -2972,22 +2975,22 @@
         <v>118</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="K18" s="43" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="L18" s="14">
         <v>2</v>
@@ -3000,7 +3003,7 @@
         <v>50</v>
       </c>
       <c r="O18" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P18" s="15">
         <v>1.7500000000000002E-2</v>
@@ -3027,22 +3030,22 @@
         <v>119</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="K19" s="44" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="L19" s="20">
         <v>7</v>
@@ -3055,7 +3058,7 @@
         <v>50</v>
       </c>
       <c r="O19" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P19" s="15">
         <v>8.3999999999999995E-3</v>
@@ -3082,22 +3085,22 @@
         <v>120</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="L20" s="14">
         <v>1</v>
@@ -3110,7 +3113,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P20" s="15">
         <v>3.7000000000000002E-3</v>
@@ -3137,22 +3140,22 @@
         <v>121</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="K21" s="44" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="L21" s="20">
         <v>2</v>
@@ -3165,7 +3168,7 @@
         <v>20</v>
       </c>
       <c r="O21" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P21" s="21">
         <v>1.83E-2</v>
@@ -3192,22 +3195,22 @@
         <v>122</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G22" s="42" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H22" s="42" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J22" s="42" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="K22" s="45" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L22" s="42">
         <v>8</v>
@@ -3217,19 +3220,19 @@
         <v>40</v>
       </c>
       <c r="N22" s="42" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="O22" s="46" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P22" s="47" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="Q22" s="47" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="R22" s="48" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -3248,22 +3251,22 @@
         <v>123</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="K23" s="44" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="L23" s="20">
         <v>2</v>
@@ -3276,7 +3279,7 @@
         <v>100</v>
       </c>
       <c r="O23" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P23" s="21">
         <v>3.0999999999999999E-3</v>
@@ -3303,22 +3306,22 @@
         <v>124</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="K24" s="43" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="L24" s="14">
         <v>3</v>
@@ -3331,7 +3334,7 @@
         <v>20</v>
       </c>
       <c r="O24" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P24" s="15">
         <v>0.29310000000000003</v>
@@ -3358,22 +3361,22 @@
         <v>125</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K25" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L25" s="20">
         <v>2</v>
@@ -3386,7 +3389,7 @@
         <v>15</v>
       </c>
       <c r="O25" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P25" s="21">
         <v>0.153</v>
@@ -3413,22 +3416,22 @@
         <v>126</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L26" s="14">
         <v>1</v>
@@ -3441,7 +3444,7 @@
         <v>10</v>
       </c>
       <c r="O26" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P26" s="15">
         <v>4.53E-2</v>
@@ -3468,22 +3471,22 @@
         <v>127</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="K27" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L27" s="20">
         <v>2</v>
@@ -3496,7 +3499,7 @@
         <v>15</v>
       </c>
       <c r="O27" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P27" s="21">
         <v>0.10249999999999999</v>
@@ -3507,7 +3510,7 @@
       </c>
       <c r="R27" s="20"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="16">
         <f>ROW(B28) - ROW($B$7)</f>
@@ -3519,26 +3522,26 @@
       <c r="D28" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>305</v>
+      <c r="E28" s="20" t="s">
+        <v>464</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>465</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>466</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>300</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>467</v>
       </c>
       <c r="K28" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L28" s="14">
         <v>2</v>
@@ -3547,12 +3550,18 @@
         <f>L28*5</f>
         <v>10</v>
       </c>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="15"/>
+      <c r="N28" s="20">
+        <v>20</v>
+      </c>
+      <c r="O28" s="49" t="s">
+        <v>451</v>
+      </c>
+      <c r="P28" s="21">
+        <v>2.4E-2</v>
+      </c>
       <c r="Q28" s="15">
         <f>P28*N28</f>
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="R28" s="14"/>
     </row>
@@ -3569,25 +3578,25 @@
         <v>48</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K29" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L29" s="20">
         <v>1</v>
@@ -3600,7 +3609,7 @@
         <v>20</v>
       </c>
       <c r="O29" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P29" s="15">
         <v>3.0800000000000001E-2</v>
@@ -3624,25 +3633,25 @@
         <v>49</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="K30" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L30" s="14">
         <v>6</v>
@@ -3655,7 +3664,7 @@
         <v>50</v>
       </c>
       <c r="O30" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P30" s="21">
         <v>2.6700000000000002E-2</v>
@@ -3679,25 +3688,25 @@
         <v>50</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="K31" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L31" s="20">
         <v>6</v>
@@ -3710,7 +3719,7 @@
         <v>50</v>
       </c>
       <c r="O31" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P31" s="15">
         <v>5.5500000000000001E-2</v>
@@ -3734,25 +3743,25 @@
         <v>51</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I32" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="J32" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="J32" s="14" t="s">
-        <v>354</v>
-      </c>
       <c r="K32" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L32" s="14">
         <v>2</v>
@@ -3765,7 +3774,7 @@
         <v>50</v>
       </c>
       <c r="O32" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P32" s="21">
         <v>7.0000000000000001E-3</v>
@@ -3789,25 +3798,25 @@
         <v>52</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G33" s="20">
         <v>1715721</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K33" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L33" s="20">
         <v>5</v>
@@ -3820,7 +3829,7 @@
         <v>26</v>
       </c>
       <c r="O33" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P33" s="15">
         <v>0.30509999999999998</v>
@@ -3844,25 +3853,25 @@
         <v>53</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K34" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L34" s="14">
         <v>1</v>
@@ -3875,7 +3884,7 @@
         <v>10</v>
       </c>
       <c r="O34" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P34" s="15">
         <v>0.1482</v>
@@ -3899,25 +3908,25 @@
         <v>54</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="K35" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L35" s="20">
         <v>1</v>
@@ -3930,7 +3939,7 @@
         <v>10</v>
       </c>
       <c r="O35" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P35" s="21">
         <v>0.10249999999999999</v>
@@ -3954,25 +3963,25 @@
         <v>55</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="K36" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L36" s="14">
         <v>1</v>
@@ -3985,7 +3994,7 @@
         <v>10</v>
       </c>
       <c r="O36" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P36" s="15">
         <v>5.1299999999999998E-2</v>
@@ -4009,25 +4018,25 @@
         <v>56</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G37" s="42" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="I37" s="20" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="K37" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L37" s="20">
         <v>1</v>
@@ -4040,7 +4049,7 @@
         <v>50</v>
       </c>
       <c r="O37" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P37" s="15">
         <v>1.4500000000000001E-2</v>
@@ -4064,25 +4073,25 @@
         <v>57</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="K38" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L38" s="14">
         <v>1</v>
@@ -4095,7 +4104,7 @@
         <v>10</v>
       </c>
       <c r="O38" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P38" s="15">
         <v>8.0100000000000005E-2</v>
@@ -4119,25 +4128,25 @@
         <v>58</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="K39" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L39" s="20">
         <v>16</v>
@@ -4150,7 +4159,7 @@
         <v>85</v>
       </c>
       <c r="O39" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P39" s="21">
         <v>7.5399999999999995E-2</v>
@@ -4174,25 +4183,25 @@
         <v>59</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="K40" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L40" s="14">
         <v>2</v>
@@ -4205,7 +4214,7 @@
         <v>16</v>
       </c>
       <c r="O40" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P40" s="15">
         <v>1.1589</v>
@@ -4229,25 +4238,25 @@
         <v>60</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="K41" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L41" s="20">
         <v>1</v>
@@ -4260,7 +4269,7 @@
         <v>10</v>
       </c>
       <c r="O41" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P41" s="15">
         <v>0.16550000000000001</v>
@@ -4284,25 +4293,25 @@
         <v>61</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="K42" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L42" s="14">
         <v>1</v>
@@ -4315,7 +4324,7 @@
         <v>10</v>
       </c>
       <c r="O42" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P42" s="21">
         <v>9.7199999999999995E-2</v>
@@ -4339,25 +4348,25 @@
         <v>62</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="K43" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L43" s="20">
         <v>1</v>
@@ -4370,7 +4379,7 @@
         <v>10</v>
       </c>
       <c r="O43" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P43" s="21">
         <v>0.22620000000000001</v>
@@ -4394,25 +4403,25 @@
         <v>63</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="K44" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L44" s="14">
         <v>4</v>
@@ -4425,7 +4434,7 @@
         <v>21</v>
       </c>
       <c r="O44" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P44" s="15">
         <v>0.66279999999999994</v>
@@ -4449,23 +4458,25 @@
         <v>64</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G45" s="20">
         <v>447690401</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="J45" s="20"/>
+        <v>346</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>468</v>
+      </c>
       <c r="K45" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L45" s="20">
         <v>16</v>
@@ -4474,12 +4485,18 @@
         <f t="shared" ref="M45" si="37">L45*5</f>
         <v>80</v>
       </c>
-      <c r="N45" s="20"/>
-      <c r="O45" s="20"/>
-      <c r="P45" s="21"/>
+      <c r="N45" s="20">
+        <v>81</v>
+      </c>
+      <c r="O45" s="50" t="s">
+        <v>451</v>
+      </c>
+      <c r="P45" s="21">
+        <v>4.3689999999999998</v>
+      </c>
       <c r="Q45" s="21">
         <f t="shared" ref="Q45" si="38">P45*N45</f>
-        <v>0</v>
+        <v>353.88900000000001</v>
       </c>
       <c r="R45" s="20"/>
     </row>
@@ -4496,25 +4513,25 @@
         <v>65</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="K46" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L46" s="14">
         <v>16</v>
@@ -4527,7 +4544,7 @@
         <v>85</v>
       </c>
       <c r="O46" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P46" s="15">
         <v>0.26779999999999998</v>
@@ -4551,25 +4568,25 @@
         <v>66</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J47" s="20" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K47" s="44" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="L47" s="20">
         <v>1</v>
@@ -4582,7 +4599,7 @@
         <v>10</v>
       </c>
       <c r="O47" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P47" s="15">
         <v>0.2757</v>
@@ -4606,25 +4623,25 @@
         <v>67</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="K48" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L48" s="14">
         <v>1</v>
@@ -4637,7 +4654,7 @@
         <v>100</v>
       </c>
       <c r="O48" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P48" s="21">
         <v>3.3E-3</v>
@@ -4661,25 +4678,25 @@
         <v>68</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J49" s="20" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="K49" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L49" s="20">
         <v>4</v>
@@ -4692,7 +4709,7 @@
         <v>40</v>
       </c>
       <c r="O49" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P49" s="15">
         <v>2.2700000000000001E-2</v>
@@ -4716,25 +4733,25 @@
         <v>69</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="K50" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L50" s="14">
         <v>1</v>
@@ -4747,7 +4764,7 @@
         <v>20</v>
       </c>
       <c r="O50" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P50" s="21">
         <v>2.3400000000000001E-2</v>
@@ -4771,25 +4788,25 @@
         <v>70</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J51" s="20" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K51" s="44" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L51" s="20">
         <v>16</v>
@@ -4802,7 +4819,7 @@
         <v>100</v>
       </c>
       <c r="O51" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P51" s="21">
         <v>3.0599999999999999E-2</v>
@@ -4826,25 +4843,25 @@
         <v>71</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="K52" s="43" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="L52" s="14">
         <v>1</v>
@@ -4857,7 +4874,7 @@
         <v>100</v>
       </c>
       <c r="O52" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P52" s="21">
         <v>1E-3</v>
@@ -4881,25 +4898,25 @@
         <v>72</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J53" s="20" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K53" s="44" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="L53" s="20">
         <v>1</v>
@@ -4912,7 +4929,7 @@
         <v>100</v>
       </c>
       <c r="O53" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P53" s="15">
         <v>4.0000000000000002E-4</v>
@@ -4936,25 +4953,25 @@
         <v>73</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I54" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="K54" s="43" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="L54" s="14">
         <v>1</v>
@@ -4967,7 +4984,7 @@
         <v>20</v>
       </c>
       <c r="O54" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P54" s="15">
         <v>2.1499999999999998E-2</v>
@@ -4991,25 +5008,25 @@
         <v>74</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G55" s="20" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J55" s="20" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="K55" s="44" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="L55" s="20">
         <v>1</v>
@@ -5022,7 +5039,7 @@
         <v>100</v>
       </c>
       <c r="O55" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P55" s="15">
         <v>5.0000000000000001E-4</v>
@@ -5046,25 +5063,25 @@
         <v>75</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I56" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="K56" s="43" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="L56" s="14">
         <v>17</v>
@@ -5077,7 +5094,7 @@
         <v>100</v>
       </c>
       <c r="O56" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P56" s="21">
         <v>5.9999999999999995E-4</v>
@@ -5101,25 +5118,25 @@
         <v>76</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J57" s="20" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="K57" s="44" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="L57" s="20">
         <v>1</v>
@@ -5132,7 +5149,7 @@
         <v>100</v>
       </c>
       <c r="O57" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P57" s="15">
         <v>6.9999999999999999E-4</v>
@@ -5154,25 +5171,25 @@
         <v>77</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="K58" s="43" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="L58" s="14">
         <v>1</v>
@@ -5185,7 +5202,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P58" s="15">
         <v>5.9999999999999995E-4</v>
@@ -5209,25 +5226,25 @@
         <v>78</v>
       </c>
       <c r="E59" s="42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F59" s="42" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G59" s="42" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H59" s="42" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I59" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J59" s="42" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="K59" s="45" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L59" s="42">
         <v>2</v>
@@ -5237,19 +5254,19 @@
         <v>10</v>
       </c>
       <c r="N59" s="42" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="O59" s="46" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P59" s="47" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="Q59" s="47" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="R59" s="48" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
@@ -5265,25 +5282,25 @@
         <v>79</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H60" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="K60" s="43" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="L60" s="14">
         <v>2</v>
@@ -5296,7 +5313,7 @@
         <v>100</v>
       </c>
       <c r="O60" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P60" s="15">
         <v>6.9999999999999999E-4</v>
@@ -5320,25 +5337,25 @@
         <v>80</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I61" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J61" s="20" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K61" s="44" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="L61" s="20">
         <v>1</v>
@@ -5351,7 +5368,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P61" s="21">
         <v>2.8E-3</v>
@@ -5375,25 +5392,25 @@
         <v>81</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="K62" s="43" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="L62" s="14">
         <v>2</v>
@@ -5406,7 +5423,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P62" s="15">
         <v>1E-3</v>
@@ -5430,25 +5447,25 @@
         <v>82</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I63" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J63" s="20" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="K63" s="44" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="L63" s="20">
         <v>11</v>
@@ -5461,7 +5478,7 @@
         <v>100</v>
       </c>
       <c r="O63" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P63" s="15">
         <v>5.0000000000000001E-4</v>
@@ -5485,25 +5502,25 @@
         <v>83</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="K64" s="43" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L64" s="14">
         <v>1</v>
@@ -5516,7 +5533,7 @@
         <v>100</v>
       </c>
       <c r="O64" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P64" s="21">
         <v>6.9999999999999999E-4</v>
@@ -5540,23 +5557,23 @@
         <v>84</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H65" s="20"/>
       <c r="I65" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J65" s="20" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="K65" s="44" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="L65" s="20">
         <v>2</v>
@@ -5569,7 +5586,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P65" s="15">
         <v>5.9999999999999995E-4</v>
@@ -5593,25 +5610,25 @@
         <v>85</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="K66" s="43" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="L66" s="14">
         <v>1</v>
@@ -5624,7 +5641,7 @@
         <v>100</v>
       </c>
       <c r="O66" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P66" s="21">
         <v>5.9999999999999995E-4</v>
@@ -5648,25 +5665,25 @@
         <v>86</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I67" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J67" s="20" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K67" s="44" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L67" s="20">
         <v>13</v>
@@ -5679,7 +5696,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P67" s="15">
         <v>6.9999999999999999E-4</v>
@@ -5703,25 +5720,25 @@
         <v>87</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H68" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I68" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J68" s="14" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="K68" s="43" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="L68" s="14">
         <v>6</v>
@@ -5734,7 +5751,7 @@
         <v>100</v>
       </c>
       <c r="O68" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P68" s="21">
         <v>8.9999999999999998E-4</v>
@@ -5758,25 +5775,25 @@
         <v>88</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J69" s="20" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="K69" s="44" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="L69" s="20">
         <v>2</v>
@@ -5789,7 +5806,7 @@
         <v>100</v>
       </c>
       <c r="O69" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P69" s="15">
         <v>1E-3</v>
@@ -5813,25 +5830,25 @@
         <v>89</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H70" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="K70" s="43" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="L70" s="14">
         <v>2</v>
@@ -5844,7 +5861,7 @@
         <v>100</v>
       </c>
       <c r="O70" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P70" s="21">
         <v>1E-3</v>
@@ -5868,25 +5885,25 @@
         <v>90</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I71" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J71" s="20" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="K71" s="44" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="L71" s="20">
         <v>1</v>
@@ -5899,7 +5916,7 @@
         <v>50</v>
       </c>
       <c r="O71" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P71" s="21">
         <v>2.0400000000000001E-2</v>
@@ -5923,25 +5940,25 @@
         <v>91</v>
       </c>
       <c r="E72" s="42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F72" s="42" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G72" s="42" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H72" s="42" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I72" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J72" s="42" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K72" s="45" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L72" s="42">
         <v>1</v>
@@ -5951,19 +5968,19 @@
         <v>5</v>
       </c>
       <c r="N72" s="42" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="O72" s="46" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P72" s="47" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="Q72" s="47" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="R72" s="48" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="24" x14ac:dyDescent="0.25">
@@ -5979,25 +5996,25 @@
         <v>92</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G73" s="20" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I73" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J73" s="20" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="K73" s="44" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="L73" s="20">
         <v>8</v>
@@ -6010,7 +6027,7 @@
         <v>100</v>
       </c>
       <c r="O73" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P73" s="15">
         <v>1.1999999999999999E-3</v>
@@ -6034,25 +6051,25 @@
         <v>93</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H74" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I74" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="K74" s="43" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="L74" s="14">
         <v>2</v>
@@ -6065,7 +6082,7 @@
         <v>100</v>
       </c>
       <c r="O74" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P74" s="21">
         <v>1E-3</v>
@@ -6089,25 +6106,25 @@
         <v>94</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G75" s="20" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I75" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J75" s="20" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="K75" s="44" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="L75" s="20">
         <v>2</v>
@@ -6120,7 +6137,7 @@
         <v>100</v>
       </c>
       <c r="O75" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P75" s="21">
         <v>6.9999999999999999E-4</v>
@@ -6144,25 +6161,25 @@
         <v>95</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H76" s="14" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="K76" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L76" s="14">
         <v>2</v>
@@ -6175,7 +6192,7 @@
         <v>20</v>
       </c>
       <c r="O76" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P76" s="15">
         <v>0.1552</v>
@@ -6199,25 +6216,25 @@
         <v>96</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I77" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J77" s="20" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="K77" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L77" s="20">
         <v>1</v>
@@ -6230,7 +6247,7 @@
         <v>6</v>
       </c>
       <c r="O77" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P77" s="15">
         <v>1.5093000000000001</v>
@@ -6254,25 +6271,25 @@
         <v>97</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H78" s="14" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I78" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="K78" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L78" s="14">
         <v>1</v>
@@ -6285,7 +6302,7 @@
         <v>10</v>
       </c>
       <c r="O78" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P78" s="15">
         <v>0.1749</v>
@@ -6309,25 +6326,25 @@
         <v>98</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I79" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J79" s="20" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="K79" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L79" s="20">
         <v>1</v>
@@ -6340,7 +6357,7 @@
         <v>6</v>
       </c>
       <c r="O79" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P79" s="21">
         <v>1.5052000000000001</v>
@@ -6364,25 +6381,25 @@
         <v>99</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H80" s="14" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I80" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="K80" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L80" s="14">
         <v>1</v>
@@ -6395,7 +6412,7 @@
         <v>6</v>
       </c>
       <c r="O80" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P80" s="21">
         <v>2.6966000000000001</v>
@@ -6419,25 +6436,25 @@
         <v>100</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J81" s="20" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="K81" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L81" s="20">
         <v>1</v>
@@ -6450,7 +6467,7 @@
         <v>6</v>
       </c>
       <c r="O81" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P81" s="15">
         <v>2.9133</v>
@@ -6474,25 +6491,25 @@
         <v>101</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G82" s="14" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H82" s="14" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I82" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="K82" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L82" s="14">
         <v>2</v>
@@ -6505,7 +6522,7 @@
         <v>11</v>
       </c>
       <c r="O82" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P82" s="15">
         <v>2.984</v>
@@ -6529,25 +6546,25 @@
         <v>102</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I83" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J83" s="20" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="K83" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L83" s="20">
         <v>1</v>
@@ -6560,7 +6577,7 @@
         <v>6</v>
       </c>
       <c r="O83" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P83" s="21">
         <v>0.33610000000000001</v>
@@ -6584,25 +6601,25 @@
         <v>103</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H84" s="14" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I84" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="K84" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L84" s="14">
         <v>1</v>
@@ -6615,7 +6632,7 @@
         <v>6</v>
       </c>
       <c r="O84" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P84" s="15">
         <v>8.6266999999999996</v>
@@ -6639,25 +6656,25 @@
         <v>104</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J85" s="20" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="K85" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L85" s="20">
         <v>3</v>
@@ -6670,7 +6687,7 @@
         <v>20</v>
       </c>
       <c r="O85" s="50" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P85" s="21">
         <v>0.20780000000000001</v>
@@ -6694,25 +6711,25 @@
         <v>105</v>
       </c>
       <c r="E86" s="42" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F86" s="42" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G86" s="42" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H86" s="42" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J86" s="42" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="K86" s="45" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L86" s="42">
         <v>1</v>
@@ -6722,19 +6739,19 @@
         <v>5</v>
       </c>
       <c r="N86" s="42" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="O86" s="46" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P86" s="47" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="Q86" s="47" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="R86" s="48" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="87" spans="1:18" ht="24" x14ac:dyDescent="0.25">
@@ -6750,25 +6767,25 @@
         <v>106</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F87" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I87" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J87" s="20" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K87" s="44" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="L87" s="20">
         <v>1</v>
@@ -6781,7 +6798,7 @@
         <v>10</v>
       </c>
       <c r="O87" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P87" s="21">
         <v>0.30080000000000001</v>
@@ -6805,25 +6822,25 @@
         <v>107</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G88" s="14" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H88" s="14" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="I88" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K88" s="43" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="L88" s="14">
         <v>1</v>
@@ -6836,7 +6853,7 @@
         <v>10</v>
       </c>
       <c r="O88" s="49" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P88" s="15">
         <v>6.5600000000000006E-2</v>
@@ -6868,7 +6885,7 @@
       <c r="P89" s="53"/>
       <c r="Q89" s="18">
         <f>SUM(Q8:Q88)</f>
-        <v>271.95909999999998</v>
+        <v>626.32809999999995</v>
       </c>
       <c r="R89" s="1"/>
     </row>
@@ -6893,7 +6910,7 @@
       <c r="P90" s="53"/>
       <c r="Q90" s="19">
         <f>Q89/5</f>
-        <v>54.391819999999996</v>
+        <v>125.26561999999998</v>
       </c>
       <c r="R90" s="1"/>
     </row>
@@ -6981,8 +6998,10 @@
     <hyperlink ref="O78" r:id="rId72"/>
     <hyperlink ref="O79" r:id="rId73"/>
     <hyperlink ref="O85" r:id="rId74"/>
+    <hyperlink ref="O28" r:id="rId75"/>
+    <hyperlink ref="O45" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId75"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId77"/>
 </worksheet>
 </file>
--- a/Design Files/Relay Driver-10A-v1.0/BOM/eSpark-BOM-Relay Driver-10A-v1.0.xlsx
+++ b/Design Files/Relay Driver-10A-v1.0/BOM/eSpark-BOM-Relay Driver-10A-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="142">
   <si>
     <t>Component list</t>
   </si>
@@ -427,6 +427,24 @@
   </si>
   <si>
     <t>----</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>Fuse</t>
+  </si>
+  <si>
+    <t>32V 1kA Blade fuse 1A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t>0287001.PXCN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Littelfuse </t>
+  </si>
+  <si>
+    <t>C142679</t>
   </si>
 </sst>
 </file>
@@ -862,6 +880,24 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -872,24 +908,6 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1179,7 +1197,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -1212,14 +1230,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1407,13 +1425,13 @@
       <c r="H8" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="K8" s="46" t="s">
+      <c r="K8" s="43" t="s">
         <v>112</v>
       </c>
       <c r="L8" s="14">
@@ -1425,13 +1443,13 @@
       <c r="N8" s="20">
         <v>25</v>
       </c>
-      <c r="O8" s="45" t="s">
+      <c r="O8" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P8" s="15">
         <v>0.29310000000000003</v>
       </c>
-      <c r="Q8" s="49">
+      <c r="Q8" s="46">
         <f>P8*N8</f>
         <v>7.3275000000000006</v>
       </c>
@@ -1440,7 +1458,7 @@
     <row r="9" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B25" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B26" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -1461,13 +1479,13 @@
       <c r="H9" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="I9" s="50" t="s">
+      <c r="I9" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J9" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="K9" s="47" t="s">
+      <c r="K9" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L9" s="20">
@@ -1480,7 +1498,7 @@
       <c r="N9" s="20">
         <v>10</v>
       </c>
-      <c r="O9" s="45" t="s">
+      <c r="O9" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P9" s="21">
@@ -1516,13 +1534,13 @@
       <c r="H10" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="I10" s="50" t="s">
+      <c r="I10" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J10" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="K10" s="47" t="s">
+      <c r="K10" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L10" s="14">
@@ -1535,7 +1553,7 @@
       <c r="N10" s="20">
         <v>10</v>
       </c>
-      <c r="O10" s="48" t="s">
+      <c r="O10" s="45" t="s">
         <v>126</v>
       </c>
       <c r="P10" s="21">
@@ -1571,13 +1589,13 @@
       <c r="H11" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I11" s="50" t="s">
+      <c r="I11" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J11" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="K11" s="47" t="s">
+      <c r="K11" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L11" s="20">
@@ -1590,7 +1608,7 @@
       <c r="N11" s="14">
         <v>10</v>
       </c>
-      <c r="O11" s="48" t="s">
+      <c r="O11" s="45" t="s">
         <v>126</v>
       </c>
       <c r="P11" s="15">
@@ -1626,13 +1644,13 @@
       <c r="H12" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="I12" s="50" t="s">
+      <c r="I12" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J12" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="K12" s="47" t="s">
+      <c r="K12" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L12" s="14">
@@ -1645,7 +1663,7 @@
       <c r="N12" s="14">
         <v>6</v>
       </c>
-      <c r="O12" s="48" t="s">
+      <c r="O12" s="45" t="s">
         <v>126</v>
       </c>
       <c r="P12" s="15">
@@ -1681,13 +1699,13 @@
       <c r="H13" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="50" t="s">
+      <c r="I13" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J13" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="K13" s="47" t="s">
+      <c r="K13" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L13" s="20">
@@ -1700,7 +1718,7 @@
       <c r="N13" s="20">
         <v>6</v>
       </c>
-      <c r="O13" s="45" t="s">
+      <c r="O13" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P13" s="21">
@@ -1736,13 +1754,13 @@
       <c r="H14" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I14" s="50" t="s">
+      <c r="I14" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J14" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="K14" s="47" t="s">
+      <c r="K14" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L14" s="14">
@@ -1755,7 +1773,7 @@
       <c r="N14" s="14">
         <v>6</v>
       </c>
-      <c r="O14" s="48" t="s">
+      <c r="O14" s="45" t="s">
         <v>126</v>
       </c>
       <c r="P14" s="15">
@@ -1791,13 +1809,13 @@
       <c r="H15" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="50" t="s">
+      <c r="I15" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J15" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="K15" s="47" t="s">
+      <c r="K15" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L15" s="20">
@@ -1810,7 +1828,7 @@
       <c r="N15" s="20">
         <v>21</v>
       </c>
-      <c r="O15" s="45" t="s">
+      <c r="O15" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P15" s="21">
@@ -1846,13 +1864,13 @@
       <c r="H16" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="I16" s="50" t="s">
+      <c r="I16" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J16" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="K16" s="47" t="s">
+      <c r="K16" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L16" s="14">
@@ -1865,7 +1883,7 @@
       <c r="N16" s="20">
         <v>21</v>
       </c>
-      <c r="O16" s="45" t="s">
+      <c r="O16" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P16" s="21">
@@ -1901,13 +1919,13 @@
       <c r="H17" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="50" t="s">
+      <c r="I17" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J17" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="K17" s="47" t="s">
+      <c r="K17" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L17" s="20">
@@ -1920,7 +1938,7 @@
       <c r="N17" s="20">
         <v>15</v>
       </c>
-      <c r="O17" s="45" t="s">
+      <c r="O17" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P17" s="21">
@@ -1956,13 +1974,13 @@
       <c r="H18" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="50" t="s">
+      <c r="I18" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J18" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="K18" s="47" t="s">
+      <c r="K18" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L18" s="14">
@@ -1975,7 +1993,7 @@
       <c r="N18" s="14">
         <v>25</v>
       </c>
-      <c r="O18" s="45" t="s">
+      <c r="O18" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P18" s="15">
@@ -2011,13 +2029,13 @@
       <c r="H19" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="I19" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J19" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="K19" s="47" t="s">
+      <c r="K19" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L19" s="20">
@@ -2030,7 +2048,7 @@
       <c r="N19" s="20">
         <v>20</v>
       </c>
-      <c r="O19" s="45" t="s">
+      <c r="O19" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P19" s="21">
@@ -2066,13 +2084,13 @@
       <c r="H20" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="50" t="s">
+      <c r="I20" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J20" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="K20" s="47" t="s">
+      <c r="K20" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L20" s="14">
@@ -2085,7 +2103,7 @@
       <c r="N20" s="14">
         <v>21</v>
       </c>
-      <c r="O20" s="45" t="s">
+      <c r="O20" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P20" s="15">
@@ -2121,13 +2139,13 @@
       <c r="H21" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="I21" s="50" t="s">
+      <c r="I21" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J21" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="K21" s="47" t="s">
+      <c r="K21" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L21" s="20">
@@ -2140,7 +2158,7 @@
       <c r="N21" s="20">
         <v>40</v>
       </c>
-      <c r="O21" s="45" t="s">
+      <c r="O21" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P21" s="21">
@@ -2176,13 +2194,13 @@
       <c r="H22" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="I22" s="50" t="s">
+      <c r="I22" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J22" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="43" t="s">
         <v>113</v>
       </c>
       <c r="L22" s="14">
@@ -2195,7 +2213,7 @@
       <c r="N22" s="14">
         <v>50</v>
       </c>
-      <c r="O22" s="45" t="s">
+      <c r="O22" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P22" s="15">
@@ -2231,13 +2249,13 @@
       <c r="H23" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="I23" s="50" t="s">
+      <c r="I23" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J23" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="K23" s="47" t="s">
+      <c r="K23" s="44" t="s">
         <v>114</v>
       </c>
       <c r="L23" s="20">
@@ -2250,7 +2268,7 @@
       <c r="N23" s="20">
         <v>100</v>
       </c>
-      <c r="O23" s="45" t="s">
+      <c r="O23" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P23" s="21">
@@ -2286,13 +2304,13 @@
       <c r="H24" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="I24" s="50" t="s">
+      <c r="I24" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J24" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="K24" s="46" t="s">
+      <c r="K24" s="43" t="s">
         <v>127</v>
       </c>
       <c r="L24" s="14">
@@ -2305,7 +2323,7 @@
       <c r="N24" s="14">
         <v>10</v>
       </c>
-      <c r="O24" s="45" t="s">
+      <c r="O24" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P24" s="15">
@@ -2317,12 +2335,9 @@
       </c>
       <c r="R24" s="14"/>
     </row>
-    <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="17">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
+      <c r="B25" s="16"/>
       <c r="C25" s="23" t="s">
         <v>18</v>
       </c>
@@ -2341,61 +2356,91 @@
       <c r="H25" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="I25" s="50" t="s">
+      <c r="I25" s="47" t="s">
         <v>135</v>
       </c>
       <c r="J25" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="K25" s="47" t="s">
+      <c r="K25" s="44" t="s">
         <v>127</v>
       </c>
       <c r="L25" s="20">
         <v>1</v>
       </c>
       <c r="M25" s="20">
-        <f t="shared" ref="M25" si="17">L25*5</f>
+        <f t="shared" ref="M25:M26" si="17">L25*5</f>
         <v>5</v>
       </c>
       <c r="N25" s="20">
         <v>10</v>
       </c>
-      <c r="O25" s="45" t="s">
+      <c r="O25" s="42" t="s">
         <v>126</v>
       </c>
       <c r="P25" s="21">
         <v>0.20780000000000001</v>
       </c>
       <c r="Q25" s="21">
-        <f t="shared" ref="Q25" si="18">P25*N25</f>
+        <f t="shared" ref="Q25:Q26" si="18">P25*N25</f>
         <v>2.0780000000000003</v>
       </c>
       <c r="R25" s="20"/>
     </row>
-    <row r="26" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="18">
-        <f>SUM(Q8:Q25)</f>
-        <v>155.29589999999996</v>
-      </c>
-      <c r="R26" s="1"/>
+      <c r="B26" s="17">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="I26" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="K26" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="L26" s="20">
+        <v>1</v>
+      </c>
+      <c r="M26" s="20">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="N26" s="20">
+        <v>5</v>
+      </c>
+      <c r="O26" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="P26" s="21">
+        <v>8.8800000000000004E-2</v>
+      </c>
+      <c r="Q26" s="21">
+        <f t="shared" si="18"/>
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="R26" s="20"/>
     </row>
     <row r="27" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
@@ -2411,25 +2456,50 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
-      <c r="N27" s="43" t="s">
+      <c r="N27" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="50"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="18">
+        <f>SUM(Q8:Q26)</f>
+        <v>155.73989999999995</v>
+      </c>
+      <c r="R27" s="1"/>
+    </row>
+    <row r="28" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="O27" s="44"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="19">
-        <f>Q26/5</f>
-        <v>31.059179999999991</v>
-      </c>
-      <c r="R27" s="1"/>
-    </row>
-    <row r="39" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M39" s="38"/>
+      <c r="O28" s="50"/>
+      <c r="P28" s="50"/>
+      <c r="Q28" s="19">
+        <f>Q27/5</f>
+        <v>31.14797999999999</v>
+      </c>
+      <c r="R28" s="1"/>
+    </row>
+    <row r="40" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M40" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N26:P26"/>
     <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N28:P28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
@@ -2450,8 +2520,9 @@
     <hyperlink ref="O23" r:id="rId16"/>
     <hyperlink ref="O24" r:id="rId17"/>
     <hyperlink ref="O25" r:id="rId18"/>
+    <hyperlink ref="O26" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId20"/>
 </worksheet>
 </file>